--- a/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$257</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$239</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10070" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9378" uniqueCount="866">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:15:21+00:00</t>
+    <t>2026-09-14T22:11:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -278,7 +278,7 @@
   </si>
   <si>
     <t>con-3:Condition.clinicalStatus SHALL be present if verificationStatus is not entered-in-error and category is problem-list-item {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
-con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}se-genetic-evidence:Genetic diagnosis must have at least one evidence.detail referencing a MolGen resource {evidence.exists() and evidence.detail.exists()}</t>
+con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>anamneseUndDiagnostik.genetischeDiagnose</t>
@@ -1061,7 +1061,7 @@
     <t>Kategorisierung als genetische Erkrankung</t>
   </si>
   <si>
-    <t>Pflicht-Kategorie zur Kennzeichnung als genetisch bestätigte Erkrankung</t>
+    <t>Pflicht-Kategorie zur Kennzeichnung als genetisch bestätigte Erkrankung. Bewusste Nutzung der extensible-Bindung von Condition.category: Der Wert bezeichnet nicht die Rolle im Datensatz, sondern macht die genetische Sicherung registeruebergreifend auswertbar.</t>
   </si>
   <si>
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
@@ -1643,6 +1643,9 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
+    <t>anamneseUndDiagnostik.genetischeDiagnose.omimCode</t>
+  </si>
+  <si>
     <t>Condition.code.coding:omim.id</t>
   </si>
   <si>
@@ -1951,7 +1954,7 @@
     <t>Beginn</t>
   </si>
   <si>
-    <t>Geschätztes oder tatsächliches Datum oder Zeitraum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung begonnen hat.</t>
   </si>
   <si>
     <t>Age is generally used when the patient reports an age at which the Condition began to occur.</t>
@@ -1991,428 +1994,105 @@
     <t>Das Datum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod</t>
-  </si>
-  <si>
-    <t>onsetPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
+    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge</t>
+  </si>
+  <si>
+    <t>onsetAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age
 </t>
   </si>
   <si>
-    <t>Beginn Zeitraum</t>
-  </si>
-  <si>
-    <t>Der Zeitraum, in dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.id</t>
+    <t>Erkrankungsbeginn als Alter</t>
+  </si>
+  <si>
+    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.id</t>
   </si>
   <si>
     <t>Condition.onset[x].id</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.extension</t>
+    <t>Condition.onset[x]:onsetAge.extension</t>
   </si>
   <si>
     <t>Condition.onset[x].extension</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von</t>
-  </si>
-  <si>
-    <t>lebensphase-von</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
+  </si>
+  <si>
+    <t>Lebensphase-Beginn</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://fhir.de/StructureDefinition/lebensphase}
 </t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.url</t>
+    <t>Lebensphase des Erkrankungsbeginns</t>
+  </si>
+  <si>
+    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.url</t>
   </si>
   <si>
     <t>http://fhir.de/StructureDefinition/lebensphase</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x]</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x]</t>
   </si>
   <si>
     <t>KlinischRelevanterZeitraum.Lebensphase.von</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Lebensphase</t>
   </si>
   <si>
     <t>http://fhir.de/ValueSet/lebensphase-de</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis</t>
-  </si>
-  <si>
-    <t>lebensphase-bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x]</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge</t>
-  </si>
-  <si>
-    <t>onsetAge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age
-</t>
-  </si>
-  <si>
-    <t>Erkrankungsbeginn als Alter</t>
-  </si>
-  <si>
-    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase des Erkrankungsbeginns</t>
-  </si>
-  <si>
-    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding.id</t>
@@ -2588,14 +2268,10 @@
     <t>Condition.abatement[x]</t>
   </si>
   <si>
-    <t>dateTime
-AgePeriodRangestring</t>
-  </si>
-  <si>
-    <t>When in resolution/remission</t>
-  </si>
-  <si>
-    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+    <t>Ende</t>
+  </si>
+  <si>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung beendet wurde.</t>
   </si>
   <si>
     <t>There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
@@ -2606,6 +2282,177 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>abatementDateTime</t>
+  </si>
+  <si>
+    <t>Ende Datum</t>
+  </si>
+  <si>
+    <t>Das Datum, an dem die Erkrankung beendet wurde.</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge</t>
+  </si>
+  <si>
+    <t>abatementAge</t>
+  </si>
+  <si>
+    <t>Erkrankungsende als Alter</t>
+  </si>
+  <si>
+    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase des Erkrankungsendes</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x]</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].code</t>
   </si>
   <si>
     <t>Condition.recordedDate</t>
@@ -3074,98 +2921,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -3183,11 +3032,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ257"/>
+  <dimension ref="A1:AQ239"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="79.40625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.20703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.52734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3363,10 +3212,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -3446,7 +3295,7 @@
         <v>80</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>81</v>
@@ -19100,7 +18949,7 @@
         <v>104</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>87</v>
+        <v>519</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>369</v>
@@ -19123,7 +18972,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>379</v>
@@ -19244,7 +19093,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>381</v>
@@ -19367,7 +19216,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>446</v>
@@ -19492,7 +19341,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>450</v>
@@ -19615,7 +19464,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>454</v>
@@ -19738,7 +19587,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>460</v>
@@ -19861,7 +19710,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>462</v>
@@ -19986,10 +19835,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20091,7 +19940,7 @@
         <v>80</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>80</v>
@@ -20111,10 +19960,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20140,13 +19989,13 @@
         <v>250</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -20175,10 +20024,10 @@
         <v>157</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>80</v>
@@ -20196,7 +20045,7 @@
         <v>80</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -20214,13 +20063,13 @@
         <v>80</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>80</v>
@@ -20229,15 +20078,15 @@
         <v>80</v>
       </c>
       <c r="AQ138" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20355,10 +20204,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20478,13 +20327,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B141" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="B141" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="C141" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>80</v>
@@ -20506,13 +20355,13 @@
         <v>80</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -20601,10 +20450,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20676,7 +20525,7 @@
         <v>80</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AC142" s="2"/>
       <c r="AD142" t="s" s="2">
@@ -20724,13 +20573,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>80</v>
@@ -20793,7 +20642,7 @@
       </c>
       <c r="Y143" s="2"/>
       <c r="Z143" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>80</v>
@@ -20849,10 +20698,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20970,10 +20819,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21093,10 +20942,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21141,7 +20990,7 @@
         <v>80</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>80</v>
@@ -21218,10 +21067,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21341,10 +21190,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21464,10 +21313,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21587,10 +21436,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21712,10 +21561,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21837,14 +21686,14 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -21863,17 +21712,17 @@
         <v>93</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>80</v>
@@ -21922,7 +21771,7 @@
         <v>80</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>92</v>
@@ -21937,22 +21786,22 @@
         <v>104</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>80</v>
@@ -21960,10 +21809,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22081,10 +21930,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22204,10 +22053,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22233,13 +22082,13 @@
         <v>106</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -22289,7 +22138,7 @@
         <v>80</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -22298,7 +22147,7 @@
         <v>92</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>104</v>
@@ -22327,10 +22176,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22356,13 +22205,13 @@
         <v>133</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -22391,10 +22240,10 @@
         <v>149</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>80</v>
@@ -22412,7 +22261,7 @@
         <v>80</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -22450,10 +22299,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22479,13 +22328,13 @@
         <v>242</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -22535,7 +22384,7 @@
         <v>80</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -22573,10 +22422,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22602,13 +22451,13 @@
         <v>106</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -22658,7 +22507,7 @@
         <v>80</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -22696,10 +22545,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22722,16 +22571,16 @@
         <v>93</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -22781,7 +22630,7 @@
         <v>80</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -22796,22 +22645,22 @@
         <v>104</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>80</v>
@@ -22819,10 +22668,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22940,10 +22789,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23063,10 +22912,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23092,13 +22941,13 @@
         <v>106</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -23148,7 +22997,7 @@
         <v>80</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -23157,7 +23006,7 @@
         <v>92</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>104</v>
@@ -23186,10 +23035,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23215,13 +23064,13 @@
         <v>133</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -23250,10 +23099,10 @@
         <v>149</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>80</v>
@@ -23271,7 +23120,7 @@
         <v>80</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -23309,10 +23158,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23338,13 +23187,13 @@
         <v>242</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23394,7 +23243,7 @@
         <v>80</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -23432,10 +23281,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23461,13 +23310,13 @@
         <v>106</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -23517,7 +23366,7 @@
         <v>80</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -23555,10 +23404,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23581,16 +23430,16 @@
         <v>93</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -23628,17 +23477,17 @@
         <v>80</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AC166" s="2"/>
       <c r="AD166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -23653,22 +23502,22 @@
         <v>104</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>80</v>
@@ -23676,13 +23525,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>80</v>
@@ -23707,13 +23556,13 @@
         <v>228</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -23763,7 +23612,7 @@
         <v>80</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23781,19 +23630,19 @@
         <v>229</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>80</v>
+        <v>632</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>80</v>
@@ -23801,13 +23650,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D168" t="s" s="2">
         <v>80</v>
@@ -23829,16 +23678,16 @@
         <v>93</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -23888,7 +23737,7 @@
         <v>80</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -23906,19 +23755,19 @@
         <v>80</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>636</v>
+        <v>80</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>80</v>
@@ -23926,10 +23775,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24047,10 +23896,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24168,14 +24017,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B171" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="B171" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="C171" s="2"/>
+      <c r="C171" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="D171" t="s" s="2">
         <v>80</v>
       </c>
@@ -24187,25 +24038,25 @@
         <v>92</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>228</v>
+        <v>644</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>644</v>
+        <v>386</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -24255,25 +24106,25 @@
         <v>80</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>646</v>
+        <v>119</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>647</v>
+        <v>80</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>648</v>
+        <v>80</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>80</v>
@@ -24282,7 +24133,7 @@
         <v>80</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>649</v>
+        <v>80</v>
       </c>
       <c r="AP171" t="s" s="2">
         <v>80</v>
@@ -24293,10 +24144,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24322,10 +24173,10 @@
         <v>106</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>652</v>
+        <v>107</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>653</v>
+        <v>108</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -24414,21 +24265,21 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>80</v>
@@ -24443,12 +24294,14 @@
         <v>112</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N173" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>80</v>
@@ -24487,7 +24340,9 @@
       <c r="AB173" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AC173" s="2"/>
+      <c r="AC173" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="AD173" t="s" s="2">
         <v>80</v>
       </c>
@@ -24504,7 +24359,7 @@
         <v>82</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>120</v>
@@ -24533,20 +24388,18 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="C174" t="s" s="2">
-        <v>657</v>
-      </c>
+        <v>652</v>
+      </c>
+      <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G174" t="s" s="2">
         <v>92</v>
@@ -24561,22 +24414,24 @@
         <v>80</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>658</v>
+        <v>133</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>385</v>
+        <v>206</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N174" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q174" s="2"/>
       <c r="R174" t="s" s="2">
-        <v>80</v>
+        <v>653</v>
       </c>
       <c r="S174" t="s" s="2">
         <v>80</v>
@@ -24618,19 +24473,19 @@
         <v>80</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>80</v>
@@ -24654,12 +24509,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="175" hidden="true">
+    <row r="175">
       <c r="A175" t="s" s="2">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24667,13 +24522,13 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G175" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>80</v>
@@ -24682,13 +24537,13 @@
         <v>80</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>106</v>
+        <v>250</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -24739,7 +24594,7 @@
         <v>80</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>109</v>
+        <v>216</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -24748,16 +24603,16 @@
         <v>92</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>80</v>
+        <v>656</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>80</v>
@@ -24777,21 +24632,21 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>80</v>
@@ -24803,17 +24658,15 @@
         <v>80</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N176" s="2"/>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>80</v>
@@ -24850,31 +24703,31 @@
         <v>80</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>80</v>
@@ -24898,26 +24751,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>80</v>
@@ -24926,16 +24779,16 @@
         <v>80</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>208</v>
+        <v>115</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -24943,7 +24796,7 @@
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>665</v>
+        <v>80</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>80</v>
@@ -24973,31 +24826,31 @@
         <v>80</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>210</v>
+        <v>119</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>80</v>
@@ -25023,10 +24876,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25046,19 +24899,23 @@
         <v>80</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>250</v>
+        <v>145</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N178" s="2"/>
-      <c r="O178" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O178" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P178" t="s" s="2">
         <v>80</v>
       </c>
@@ -25082,13 +24939,13 @@
         <v>80</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>80</v>
+        <v>663</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>80</v>
+        <v>664</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>80</v>
@@ -25106,13 +24963,13 @@
         <v>80</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>199</v>
@@ -25124,7 +24981,7 @@
         <v>80</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>668</v>
+        <v>80</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>80</v>
@@ -25133,7 +24990,7 @@
         <v>80</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="AP178" t="s" s="2">
         <v>80</v>
@@ -25144,10 +25001,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -25265,10 +25122,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25388,10 +25245,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25414,19 +25271,19 @@
         <v>93</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>80</v>
@@ -25451,13 +25308,13 @@
         <v>80</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>675</v>
+        <v>80</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>676</v>
+        <v>80</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>80</v>
@@ -25475,13 +25332,13 @@
         <v>80</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>199</v>
@@ -25502,7 +25359,7 @@
         <v>80</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="AP181" t="s" s="2">
         <v>80</v>
@@ -25513,10 +25370,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -25536,18 +25393,20 @@
         <v>80</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K182" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>107</v>
+        <v>282</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N182" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>80</v>
@@ -25596,7 +25455,7 @@
         <v>80</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>109</v>
+        <v>285</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -25605,10 +25464,10 @@
         <v>92</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>80</v>
@@ -25623,7 +25482,7 @@
         <v>80</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="AP182" t="s" s="2">
         <v>80</v>
@@ -25632,46 +25491,48 @@
         <v>80</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>113</v>
+        <v>288</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>114</v>
+        <v>289</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O183" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>80</v>
       </c>
@@ -25707,31 +25568,31 @@
         <v>80</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>119</v>
+        <v>291</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>199</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>80</v>
@@ -25746,7 +25607,7 @@
         <v>80</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AP183" t="s" s="2">
         <v>80</v>
@@ -25755,12 +25616,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25768,13 +25629,13 @@
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G184" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H184" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I184" t="s" s="2">
         <v>80</v>
@@ -25783,19 +25644,19 @@
         <v>93</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>277</v>
+        <v>407</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>80</v>
@@ -25844,7 +25705,7 @@
         <v>80</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -25871,7 +25732,7 @@
         <v>80</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="AP184" t="s" s="2">
         <v>80</v>
@@ -25882,10 +25743,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25908,18 +25769,20 @@
         <v>93</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>80</v>
       </c>
@@ -25967,7 +25830,7 @@
         <v>80</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -25994,7 +25857,7 @@
         <v>80</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="AP185" t="s" s="2">
         <v>80</v>
@@ -26003,12 +25866,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26016,13 +25879,13 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G186" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>80</v>
@@ -26031,19 +25894,19 @@
         <v>93</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>407</v>
+        <v>310</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>80</v>
@@ -26092,7 +25955,7 @@
         <v>80</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -26119,7 +25982,7 @@
         <v>80</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="AP186" t="s" s="2">
         <v>80</v>
@@ -26130,10 +25993,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26156,19 +26019,19 @@
         <v>93</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>106</v>
+        <v>683</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>294</v>
+        <v>684</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>295</v>
+        <v>685</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>407</v>
+        <v>686</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>296</v>
+        <v>687</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>80</v>
@@ -26217,7 +26080,7 @@
         <v>80</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>297</v>
+        <v>688</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -26226,7 +26089,7 @@
         <v>92</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>104</v>
@@ -26244,7 +26107,7 @@
         <v>80</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>298</v>
+        <v>689</v>
       </c>
       <c r="AP187" t="s" s="2">
         <v>80</v>
@@ -26255,10 +26118,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -26275,30 +26138,30 @@
         <v>80</v>
       </c>
       <c r="I188" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J188" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>300</v>
+        <v>167</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>301</v>
+        <v>692</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>304</v>
+        <v>694</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q188" s="2"/>
+      <c r="Q188" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="R188" t="s" s="2">
         <v>80</v>
       </c>
@@ -26318,13 +26181,13 @@
         <v>80</v>
       </c>
       <c r="X188" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>80</v>
+        <v>696</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>80</v>
+        <v>697</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>80</v>
@@ -26342,7 +26205,7 @@
         <v>80</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>305</v>
+        <v>698</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -26351,7 +26214,7 @@
         <v>92</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>104</v>
@@ -26369,7 +26232,7 @@
         <v>80</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>306</v>
+        <v>699</v>
       </c>
       <c r="AP188" t="s" s="2">
         <v>80</v>
@@ -26380,10 +26243,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26409,16 +26272,14 @@
         <v>106</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>308</v>
+        <v>702</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>311</v>
+        <v>704</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>80</v>
@@ -26467,7 +26328,7 @@
         <v>80</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>312</v>
+        <v>705</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -26476,7 +26337,7 @@
         <v>92</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>104</v>
@@ -26494,7 +26355,7 @@
         <v>80</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>313</v>
+        <v>706</v>
       </c>
       <c r="AP189" t="s" s="2">
         <v>80</v>
@@ -26505,10 +26366,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26528,19 +26389,21 @@
         <v>80</v>
       </c>
       <c r="J190" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>228</v>
+        <v>133</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>696</v>
+        <v>710</v>
       </c>
       <c r="N190" s="2"/>
-      <c r="O190" s="2"/>
+      <c r="O190" t="s" s="2">
+        <v>711</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>80</v>
       </c>
@@ -26588,7 +26451,7 @@
         <v>80</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>697</v>
+        <v>712</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -26597,10 +26460,10 @@
         <v>92</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>80</v>
+        <v>713</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>80</v>
@@ -26615,7 +26478,7 @@
         <v>80</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>80</v>
+        <v>706</v>
       </c>
       <c r="AP190" t="s" s="2">
         <v>80</v>
@@ -26624,12 +26487,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>699</v>
+        <v>715</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26643,7 +26506,7 @@
         <v>92</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>80</v>
@@ -26652,24 +26515,24 @@
         <v>93</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>228</v>
+        <v>167</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>701</v>
+        <v>717</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="O191" s="2"/>
+        <v>718</v>
+      </c>
+      <c r="O191" t="s" s="2">
+        <v>719</v>
+      </c>
       <c r="P191" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q191" t="s" s="2">
-        <v>703</v>
-      </c>
+      <c r="Q191" s="2"/>
       <c r="R191" t="s" s="2">
         <v>80</v>
       </c>
@@ -26713,7 +26576,7 @@
         <v>80</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>704</v>
+        <v>720</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -26722,7 +26585,7 @@
         <v>92</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>647</v>
+        <v>80</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>104</v>
@@ -26731,7 +26594,7 @@
         <v>80</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>705</v>
+        <v>80</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>80</v>
@@ -26751,10 +26614,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>708</v>
+        <v>721</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26768,7 +26631,7 @@
         <v>92</v>
       </c>
       <c r="H192" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I192" t="s" s="2">
         <v>80</v>
@@ -26777,15 +26640,17 @@
         <v>80</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>106</v>
+        <v>617</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>652</v>
+        <v>722</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N192" s="2"/>
+        <v>723</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>724</v>
+      </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>80</v>
@@ -26822,19 +26687,17 @@
         <v>80</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="AC192" s="2"/>
       <c r="AD192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>109</v>
+        <v>721</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -26843,16 +26706,16 @@
         <v>92</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>80</v>
+        <v>725</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>80</v>
+        <v>624</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>80</v>
@@ -26864,20 +26727,22 @@
         <v>80</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>80</v>
+        <v>726</v>
       </c>
       <c r="AQ192" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="193" hidden="true">
+    <row r="193">
       <c r="A193" t="s" s="2">
-        <v>709</v>
+        <v>727</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C193" s="2"/>
+        <v>721</v>
+      </c>
+      <c r="C193" t="s" s="2">
+        <v>728</v>
+      </c>
       <c r="D193" t="s" s="2">
         <v>80</v>
       </c>
@@ -26886,10 +26751,10 @@
         <v>81</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H193" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I193" t="s" s="2">
         <v>80</v>
@@ -26898,15 +26763,17 @@
         <v>80</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>190</v>
+        <v>729</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N193" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>724</v>
+      </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>80</v>
@@ -26943,35 +26810,37 @@
         <v>80</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC193" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>119</v>
+        <v>721</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>80</v>
+        <v>725</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>80</v>
+        <v>731</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>80</v>
@@ -26983,7 +26852,7 @@
         <v>80</v>
       </c>
       <c r="AP193" t="s" s="2">
-        <v>80</v>
+        <v>726</v>
       </c>
       <c r="AQ193" t="s" s="2">
         <v>80</v>
@@ -26991,13 +26860,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>712</v>
+        <v>733</v>
       </c>
       <c r="D194" t="s" s="2">
         <v>80</v>
@@ -27019,15 +26888,17 @@
         <v>80</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>658</v>
+        <v>635</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>385</v>
+        <v>734</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N194" s="2"/>
+        <v>735</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>724</v>
+      </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
         <v>80</v>
@@ -27076,19 +26947,19 @@
         <v>80</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>119</v>
+        <v>721</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>199</v>
+        <v>725</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>80</v>
@@ -27106,7 +26977,7 @@
         <v>80</v>
       </c>
       <c r="AP194" t="s" s="2">
-        <v>80</v>
+        <v>726</v>
       </c>
       <c r="AQ194" t="s" s="2">
         <v>80</v>
@@ -27114,10 +26985,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>713</v>
+        <v>736</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>714</v>
+        <v>737</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27235,10 +27106,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>715</v>
+        <v>738</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>716</v>
+        <v>739</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -27249,7 +27120,7 @@
         <v>81</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>80</v>
@@ -27329,7 +27200,7 @@
         <v>82</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>120</v>
@@ -27356,26 +27227,28 @@
         <v>80</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>717</v>
+        <v>740</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="C197" s="2"/>
+        <v>739</v>
+      </c>
+      <c r="C197" t="s" s="2">
+        <v>741</v>
+      </c>
       <c r="D197" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G197" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H197" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I197" t="s" s="2">
         <v>80</v>
@@ -27384,16 +27257,16 @@
         <v>80</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>133</v>
+        <v>644</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>206</v>
+        <v>742</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>207</v>
+        <v>386</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>208</v>
+        <v>646</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -27401,7 +27274,7 @@
       </c>
       <c r="Q197" s="2"/>
       <c r="R197" t="s" s="2">
-        <v>665</v>
+        <v>80</v>
       </c>
       <c r="S197" t="s" s="2">
         <v>80</v>
@@ -27443,19 +27316,19 @@
         <v>80</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>210</v>
+        <v>119</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH197" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI197" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK197" t="s" s="2">
         <v>80</v>
@@ -27479,12 +27352,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>719</v>
+        <v>743</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>720</v>
+        <v>744</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27492,13 +27365,13 @@
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G198" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H198" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I198" t="s" s="2">
         <v>80</v>
@@ -27507,13 +27380,13 @@
         <v>80</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>250</v>
+        <v>106</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>215</v>
+        <v>108</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -27564,7 +27437,7 @@
         <v>80</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -27573,16 +27446,16 @@
         <v>92</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK198" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>721</v>
+        <v>80</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>80</v>
@@ -27602,21 +27475,21 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>722</v>
+        <v>745</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>723</v>
+        <v>746</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H199" t="s" s="2">
         <v>80</v>
@@ -27628,15 +27501,17 @@
         <v>80</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N199" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N199" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
         <v>80</v>
@@ -27673,31 +27548,31 @@
         <v>80</v>
       </c>
       <c r="AB199" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AC199" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AD199" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE199" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>80</v>
@@ -27721,26 +27596,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="200" hidden="true">
+    <row r="200">
       <c r="A200" t="s" s="2">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>725</v>
+        <v>748</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H200" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I200" t="s" s="2">
         <v>80</v>
@@ -27749,16 +27624,16 @@
         <v>80</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>113</v>
+        <v>206</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -27766,7 +27641,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>80</v>
+        <v>653</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>80</v>
@@ -27796,31 +27671,31 @@
         <v>80</v>
       </c>
       <c r="AB200" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC200" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD200" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="AG200" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AK200" t="s" s="2">
         <v>80</v>
@@ -27846,10 +27721,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>727</v>
+        <v>750</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27869,23 +27744,19 @@
         <v>80</v>
       </c>
       <c r="J201" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>266</v>
+        <v>214</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O201" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N201" s="2"/>
+      <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
         <v>80</v>
       </c>
@@ -27909,13 +27780,13 @@
         <v>80</v>
       </c>
       <c r="X201" t="s" s="2">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>675</v>
+        <v>80</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>676</v>
+        <v>80</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>80</v>
@@ -27933,13 +27804,13 @@
         <v>80</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>270</v>
+        <v>216</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI201" t="s" s="2">
         <v>199</v>
@@ -27951,7 +27822,7 @@
         <v>80</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>80</v>
+        <v>751</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>80</v>
@@ -27960,7 +27831,7 @@
         <v>80</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>80</v>
@@ -27971,10 +27842,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>728</v>
+        <v>752</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>729</v>
+        <v>753</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28092,10 +27963,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>730</v>
+        <v>754</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>731</v>
+        <v>755</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28215,10 +28086,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>733</v>
+        <v>757</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -28241,19 +28112,19 @@
         <v>93</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>80</v>
@@ -28278,13 +28149,13 @@
         <v>80</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>80</v>
+        <v>663</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>80</v>
+        <v>664</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>80</v>
@@ -28302,13 +28173,13 @@
         <v>80</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>199</v>
@@ -28329,7 +28200,7 @@
         <v>80</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AP204" t="s" s="2">
         <v>80</v>
@@ -28340,10 +28211,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>734</v>
+        <v>758</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>735</v>
+        <v>759</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -28363,20 +28234,18 @@
         <v>80</v>
       </c>
       <c r="J205" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K205" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N205" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N205" s="2"/>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
         <v>80</v>
@@ -28425,7 +28294,7 @@
         <v>80</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>285</v>
+        <v>109</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -28434,10 +28303,10 @@
         <v>92</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK205" t="s" s="2">
         <v>80</v>
@@ -28452,7 +28321,7 @@
         <v>80</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>286</v>
+        <v>80</v>
       </c>
       <c r="AP205" t="s" s="2">
         <v>80</v>
@@ -28461,48 +28330,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>736</v>
+        <v>760</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>737</v>
+        <v>761</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H206" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>288</v>
+        <v>113</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>289</v>
+        <v>114</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>80</v>
       </c>
@@ -28538,31 +28405,31 @@
         <v>80</v>
       </c>
       <c r="AB206" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AC206" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AD206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE206" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>291</v>
+        <v>119</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>199</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>80</v>
@@ -28577,7 +28444,7 @@
         <v>80</v>
       </c>
       <c r="AO206" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="AP206" t="s" s="2">
         <v>80</v>
@@ -28586,12 +28453,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="207" hidden="true">
+    <row r="207">
       <c r="A207" t="s" s="2">
-        <v>738</v>
+        <v>762</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>739</v>
+        <v>763</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28599,13 +28466,13 @@
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G207" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H207" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I207" t="s" s="2">
         <v>80</v>
@@ -28614,19 +28481,19 @@
         <v>93</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>407</v>
+        <v>277</v>
       </c>
       <c r="O207" t="s" s="2">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>80</v>
@@ -28675,7 +28542,7 @@
         <v>80</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -28702,7 +28569,7 @@
         <v>80</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="AP207" t="s" s="2">
         <v>80</v>
@@ -28713,10 +28580,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>740</v>
+        <v>764</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>741</v>
+        <v>765</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28739,20 +28606,18 @@
         <v>93</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>300</v>
+        <v>106</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O208" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>80</v>
       </c>
@@ -28800,7 +28665,7 @@
         <v>80</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28827,7 +28692,7 @@
         <v>80</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AP208" t="s" s="2">
         <v>80</v>
@@ -28836,12 +28701,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="209" hidden="true">
+    <row r="209">
       <c r="A209" t="s" s="2">
-        <v>742</v>
+        <v>766</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>743</v>
+        <v>767</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28849,13 +28714,13 @@
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G209" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H209" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I209" t="s" s="2">
         <v>80</v>
@@ -28864,19 +28729,19 @@
         <v>93</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>310</v>
+        <v>407</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>80</v>
@@ -28925,7 +28790,7 @@
         <v>80</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -28952,7 +28817,7 @@
         <v>80</v>
       </c>
       <c r="AO209" t="s" s="2">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="AP209" t="s" s="2">
         <v>80</v>
@@ -28963,10 +28828,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>744</v>
+        <v>768</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>745</v>
+        <v>769</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28986,19 +28851,23 @@
         <v>80</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>228</v>
+        <v>106</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>695</v>
+        <v>294</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="N210" s="2"/>
-      <c r="O210" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O210" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P210" t="s" s="2">
         <v>80</v>
       </c>
@@ -29046,7 +28915,7 @@
         <v>80</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>697</v>
+        <v>297</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -29055,10 +28924,10 @@
         <v>92</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>80</v>
@@ -29073,7 +28942,7 @@
         <v>80</v>
       </c>
       <c r="AO210" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AP210" t="s" s="2">
         <v>80</v>
@@ -29082,16 +28951,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>746</v>
+        <v>770</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="C211" t="s" s="2">
-        <v>747</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
         <v>80</v>
       </c>
@@ -29103,7 +28970,7 @@
         <v>92</v>
       </c>
       <c r="H211" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I211" t="s" s="2">
         <v>80</v>
@@ -29112,18 +28979,20 @@
         <v>93</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>748</v>
+        <v>300</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>749</v>
+        <v>301</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>750</v>
+        <v>302</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="O211" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O211" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P211" t="s" s="2">
         <v>80</v>
       </c>
@@ -29171,7 +29040,7 @@
         <v>80</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>615</v>
+        <v>305</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -29180,7 +29049,7 @@
         <v>92</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ211" t="s" s="2">
         <v>104</v>
@@ -29192,16 +29061,16 @@
         <v>80</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>624</v>
+        <v>80</v>
       </c>
       <c r="AN211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO211" t="s" s="2">
-        <v>625</v>
+        <v>306</v>
       </c>
       <c r="AP211" t="s" s="2">
-        <v>626</v>
+        <v>80</v>
       </c>
       <c r="AQ211" t="s" s="2">
         <v>80</v>
@@ -29209,10 +29078,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>638</v>
+        <v>773</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -29232,19 +29101,23 @@
         <v>80</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K212" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>107</v>
+        <v>308</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N212" s="2"/>
-      <c r="O212" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O212" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P212" t="s" s="2">
         <v>80</v>
       </c>
@@ -29292,7 +29165,7 @@
         <v>80</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>109</v>
+        <v>312</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
@@ -29301,10 +29174,10 @@
         <v>92</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>80</v>
@@ -29319,7 +29192,7 @@
         <v>80</v>
       </c>
       <c r="AO212" t="s" s="2">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="AP212" t="s" s="2">
         <v>80</v>
@@ -29330,21 +29203,21 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>640</v>
+        <v>775</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>80</v>
@@ -29353,21 +29226,23 @@
         <v>80</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>112</v>
+        <v>683</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>113</v>
+        <v>684</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>114</v>
+        <v>685</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O213" s="2"/>
+        <v>686</v>
+      </c>
+      <c r="O213" t="s" s="2">
+        <v>687</v>
+      </c>
       <c r="P213" t="s" s="2">
         <v>80</v>
       </c>
@@ -29403,31 +29278,31 @@
         <v>80</v>
       </c>
       <c r="AB213" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC213" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD213" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE213" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>119</v>
+        <v>688</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>80</v>
@@ -29442,7 +29317,7 @@
         <v>80</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>80</v>
+        <v>689</v>
       </c>
       <c r="AP213" t="s" s="2">
         <v>80</v>
@@ -29453,14 +29328,12 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>753</v>
+        <v>776</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="C214" t="s" s="2">
-        <v>754</v>
-      </c>
+        <v>777</v>
+      </c>
+      <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
         <v>80</v>
       </c>
@@ -29475,28 +29348,30 @@
         <v>80</v>
       </c>
       <c r="I214" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>658</v>
+        <v>167</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>755</v>
+        <v>692</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="O214" s="2"/>
+        <v>693</v>
+      </c>
+      <c r="N214" s="2"/>
+      <c r="O214" t="s" s="2">
+        <v>694</v>
+      </c>
       <c r="P214" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q214" s="2"/>
+      <c r="Q214" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="R214" t="s" s="2">
         <v>80</v>
       </c>
@@ -29516,13 +29391,13 @@
         <v>80</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>80</v>
+        <v>696</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>80</v>
+        <v>697</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>80</v>
@@ -29540,19 +29415,19 @@
         <v>80</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>119</v>
+        <v>698</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>80</v>
@@ -29567,7 +29442,7 @@
         <v>80</v>
       </c>
       <c r="AO214" t="s" s="2">
-        <v>80</v>
+        <v>699</v>
       </c>
       <c r="AP214" t="s" s="2">
         <v>80</v>
@@ -29578,10 +29453,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -29601,19 +29476,21 @@
         <v>80</v>
       </c>
       <c r="J215" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K215" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>107</v>
+        <v>702</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>108</v>
+        <v>703</v>
       </c>
       <c r="N215" s="2"/>
-      <c r="O215" s="2"/>
+      <c r="O215" t="s" s="2">
+        <v>704</v>
+      </c>
       <c r="P215" t="s" s="2">
         <v>80</v>
       </c>
@@ -29661,7 +29538,7 @@
         <v>80</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>109</v>
+        <v>705</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -29673,7 +29550,7 @@
         <v>80</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>80</v>
@@ -29688,7 +29565,7 @@
         <v>80</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>80</v>
+        <v>706</v>
       </c>
       <c r="AP215" t="s" s="2">
         <v>80</v>
@@ -29699,21 +29576,21 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>759</v>
+        <v>780</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>80</v>
@@ -29722,21 +29599,21 @@
         <v>80</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>113</v>
+        <v>709</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N216" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O216" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="N216" s="2"/>
+      <c r="O216" t="s" s="2">
+        <v>711</v>
+      </c>
       <c r="P216" t="s" s="2">
         <v>80</v>
       </c>
@@ -29772,31 +29649,31 @@
         <v>80</v>
       </c>
       <c r="AB216" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC216" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD216" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>119</v>
+        <v>712</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>199</v>
+        <v>713</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>80</v>
@@ -29811,7 +29688,7 @@
         <v>80</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>80</v>
+        <v>706</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>80</v>
@@ -29820,12 +29697,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>762</v>
+        <v>783</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29833,39 +29710,41 @@
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G217" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H217" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I217" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J217" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I217" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J217" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K217" t="s" s="2">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>206</v>
+        <v>716</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>207</v>
+        <v>717</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O217" s="2"/>
+        <v>718</v>
+      </c>
+      <c r="O217" t="s" s="2">
+        <v>719</v>
+      </c>
       <c r="P217" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q217" s="2"/>
       <c r="R217" t="s" s="2">
-        <v>665</v>
+        <v>80</v>
       </c>
       <c r="S217" t="s" s="2">
         <v>80</v>
@@ -29907,10 +29786,10 @@
         <v>80</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>210</v>
+        <v>720</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>92</v>
@@ -29919,7 +29798,7 @@
         <v>80</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>80</v>
@@ -29934,7 +29813,7 @@
         <v>80</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>80</v>
+        <v>706</v>
       </c>
       <c r="AP217" t="s" s="2">
         <v>80</v>
@@ -29945,10 +29824,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29968,16 +29847,16 @@
         <v>80</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>214</v>
+        <v>785</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>215</v>
+        <v>786</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -30028,7 +29907,7 @@
         <v>80</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>216</v>
+        <v>784</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -30037,7 +29916,7 @@
         <v>92</v>
       </c>
       <c r="AI218" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ218" t="s" s="2">
         <v>104</v>
@@ -30046,7 +29925,7 @@
         <v>80</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>80</v>
+        <v>787</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>80</v>
@@ -30055,21 +29934,21 @@
         <v>80</v>
       </c>
       <c r="AO218" t="s" s="2">
-        <v>80</v>
+        <v>788</v>
       </c>
       <c r="AP218" t="s" s="2">
-        <v>80</v>
+        <v>789</v>
       </c>
       <c r="AQ218" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="219" hidden="true">
+    <row r="219">
       <c r="A219" t="s" s="2">
-        <v>765</v>
+        <v>790</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>766</v>
+        <v>790</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -30083,22 +29962,22 @@
         <v>92</v>
       </c>
       <c r="H219" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>106</v>
+        <v>791</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>107</v>
+        <v>792</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>108</v>
+        <v>793</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -30149,7 +30028,7 @@
         <v>80</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>109</v>
+        <v>790</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -30161,7 +30040,7 @@
         <v>80</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>80</v>
@@ -30179,51 +30058,49 @@
         <v>80</v>
       </c>
       <c r="AP219" t="s" s="2">
-        <v>80</v>
+        <v>794</v>
       </c>
       <c r="AQ219" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="220" hidden="true">
+    <row r="220">
       <c r="A220" t="s" s="2">
-        <v>767</v>
+        <v>795</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G220" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H220" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I220" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>112</v>
+        <v>791</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>113</v>
+        <v>796</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N220" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>797</v>
+      </c>
+      <c r="N220" s="2"/>
       <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
         <v>80</v>
@@ -30260,31 +30137,31 @@
         <v>80</v>
       </c>
       <c r="AB220" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC220" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD220" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE220" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>119</v>
+        <v>795</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK220" t="s" s="2">
         <v>80</v>
@@ -30299,10 +30176,10 @@
         <v>80</v>
       </c>
       <c r="AO220" t="s" s="2">
-        <v>80</v>
+        <v>798</v>
       </c>
       <c r="AP220" t="s" s="2">
-        <v>80</v>
+        <v>799</v>
       </c>
       <c r="AQ220" t="s" s="2">
         <v>80</v>
@@ -30310,10 +30187,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>769</v>
+        <v>800</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -30321,10 +30198,10 @@
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H221" t="s" s="2">
         <v>93</v>
@@ -30333,23 +30210,19 @@
         <v>80</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>145</v>
+        <v>801</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>266</v>
+        <v>802</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O221" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>803</v>
+      </c>
+      <c r="N221" s="2"/>
+      <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
         <v>80</v>
       </c>
@@ -30373,13 +30246,13 @@
         <v>80</v>
       </c>
       <c r="X221" t="s" s="2">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="Y221" t="s" s="2">
-        <v>675</v>
+        <v>80</v>
       </c>
       <c r="Z221" t="s" s="2">
-        <v>676</v>
+        <v>80</v>
       </c>
       <c r="AA221" t="s" s="2">
         <v>80</v>
@@ -30397,7 +30270,7 @@
         <v>80</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>270</v>
+        <v>800</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -30406,10 +30279,10 @@
         <v>82</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>104</v>
+        <v>804</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>80</v>
@@ -30424,7 +30297,7 @@
         <v>80</v>
       </c>
       <c r="AO221" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AP221" t="s" s="2">
         <v>80</v>
@@ -30435,10 +30308,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>771</v>
+        <v>805</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>772</v>
+        <v>805</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -30556,10 +30429,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>773</v>
+        <v>806</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>774</v>
+        <v>806</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -30629,16 +30502,16 @@
         <v>80</v>
       </c>
       <c r="AB223" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC223" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD223" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE223" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF223" t="s" s="2">
         <v>119</v>
@@ -30650,7 +30523,7 @@
         <v>82</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ223" t="s" s="2">
         <v>120</v>
@@ -30677,47 +30550,47 @@
         <v>80</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>775</v>
+        <v>807</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>776</v>
+        <v>807</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>80</v>
+        <v>808</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H224" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I224" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="I224" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J224" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>275</v>
+        <v>809</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>276</v>
+        <v>810</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>277</v>
+        <v>115</v>
       </c>
       <c r="O224" t="s" s="2">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>80</v>
@@ -30766,19 +30639,19 @@
         <v>80</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>279</v>
+        <v>811</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK224" t="s" s="2">
         <v>80</v>
@@ -30793,7 +30666,7 @@
         <v>80</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AP224" t="s" s="2">
         <v>80</v>
@@ -30804,10 +30677,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>777</v>
+        <v>812</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>778</v>
+        <v>812</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30827,20 +30700,18 @@
         <v>80</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>106</v>
+        <v>250</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>282</v>
+        <v>813</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>814</v>
+      </c>
+      <c r="N225" s="2"/>
       <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
         <v>80</v>
@@ -30865,13 +30736,13 @@
         <v>80</v>
       </c>
       <c r="X225" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="Y225" t="s" s="2">
-        <v>80</v>
+        <v>815</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>80</v>
+        <v>816</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>80</v>
@@ -30889,7 +30760,7 @@
         <v>80</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>285</v>
+        <v>812</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -30898,7 +30769,7 @@
         <v>92</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>199</v>
+        <v>817</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>104</v>
@@ -30913,10 +30784,10 @@
         <v>80</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>80</v>
+        <v>818</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="AP225" t="s" s="2">
         <v>80</v>
@@ -30925,12 +30796,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>779</v>
+        <v>819</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30938,35 +30809,31 @@
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G226" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H226" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I226" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>167</v>
+        <v>820</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>288</v>
+        <v>821</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O226" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>822</v>
+      </c>
+      <c r="N226" s="2"/>
+      <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>80</v>
       </c>
@@ -31014,16 +30881,16 @@
         <v>80</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>291</v>
+        <v>819</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH226" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>199</v>
+        <v>817</v>
       </c>
       <c r="AJ226" t="s" s="2">
         <v>104</v>
@@ -31041,7 +30908,7 @@
         <v>80</v>
       </c>
       <c r="AO226" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="AP226" t="s" s="2">
         <v>80</v>
@@ -31052,10 +30919,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>781</v>
+        <v>823</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>782</v>
+        <v>823</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -31075,23 +30942,19 @@
         <v>80</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>106</v>
+        <v>250</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>294</v>
+        <v>824</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O227" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>825</v>
+      </c>
+      <c r="N227" s="2"/>
+      <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
         <v>80</v>
       </c>
@@ -31115,13 +30978,13 @@
         <v>80</v>
       </c>
       <c r="X227" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="Y227" t="s" s="2">
-        <v>80</v>
+        <v>826</v>
       </c>
       <c r="Z227" t="s" s="2">
-        <v>80</v>
+        <v>827</v>
       </c>
       <c r="AA227" t="s" s="2">
         <v>80</v>
@@ -31139,7 +31002,7 @@
         <v>80</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>297</v>
+        <v>823</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -31148,7 +31011,7 @@
         <v>92</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ227" t="s" s="2">
         <v>104</v>
@@ -31166,7 +31029,7 @@
         <v>80</v>
       </c>
       <c r="AO227" t="s" s="2">
-        <v>298</v>
+        <v>80</v>
       </c>
       <c r="AP227" t="s" s="2">
         <v>80</v>
@@ -31175,12 +31038,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="228" hidden="true">
+    <row r="228">
       <c r="A228" t="s" s="2">
-        <v>783</v>
+        <v>828</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>784</v>
+        <v>828</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -31188,35 +31051,33 @@
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H228" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I228" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J228" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>300</v>
+        <v>801</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>301</v>
+        <v>829</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>302</v>
+        <v>830</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O228" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>831</v>
+      </c>
+      <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
         <v>80</v>
       </c>
@@ -31264,19 +31125,19 @@
         <v>80</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>305</v>
+        <v>828</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI228" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>104</v>
+        <v>832</v>
       </c>
       <c r="AK228" t="s" s="2">
         <v>80</v>
@@ -31291,7 +31152,7 @@
         <v>80</v>
       </c>
       <c r="AO228" t="s" s="2">
-        <v>306</v>
+        <v>80</v>
       </c>
       <c r="AP228" t="s" s="2">
         <v>80</v>
@@ -31302,10 +31163,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>785</v>
+        <v>833</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>786</v>
+        <v>833</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -31325,23 +31186,19 @@
         <v>80</v>
       </c>
       <c r="J229" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K229" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>308</v>
+        <v>107</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N229" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N229" s="2"/>
+      <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
         <v>80</v>
       </c>
@@ -31389,7 +31246,7 @@
         <v>80</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>312</v>
+        <v>109</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -31398,10 +31255,10 @@
         <v>92</v>
       </c>
       <c r="AI229" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK229" t="s" s="2">
         <v>80</v>
@@ -31416,7 +31273,7 @@
         <v>80</v>
       </c>
       <c r="AO229" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="AP229" t="s" s="2">
         <v>80</v>
@@ -31427,21 +31284,21 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>787</v>
+        <v>834</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>788</v>
+        <v>834</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>80</v>
@@ -31450,23 +31307,21 @@
         <v>80</v>
       </c>
       <c r="J230" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>789</v>
+        <v>112</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>790</v>
+        <v>113</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>791</v>
+        <v>114</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="O230" t="s" s="2">
-        <v>793</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
         <v>80</v>
       </c>
@@ -31514,19 +31369,19 @@
         <v>80</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>794</v>
+        <v>119</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK230" t="s" s="2">
         <v>80</v>
@@ -31541,7 +31396,7 @@
         <v>80</v>
       </c>
       <c r="AO230" t="s" s="2">
-        <v>795</v>
+        <v>80</v>
       </c>
       <c r="AP230" t="s" s="2">
         <v>80</v>
@@ -31552,21 +31407,21 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>796</v>
+        <v>835</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>797</v>
+        <v>835</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>80</v>
+        <v>808</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>80</v>
@@ -31578,24 +31433,24 @@
         <v>93</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="N231" s="2"/>
+        <v>810</v>
+      </c>
+      <c r="N231" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O231" t="s" s="2">
-        <v>800</v>
+        <v>239</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q231" t="s" s="2">
-        <v>801</v>
-      </c>
+      <c r="Q231" s="2"/>
       <c r="R231" t="s" s="2">
         <v>80</v>
       </c>
@@ -31615,13 +31470,13 @@
         <v>80</v>
       </c>
       <c r="X231" t="s" s="2">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="Y231" t="s" s="2">
-        <v>802</v>
+        <v>80</v>
       </c>
       <c r="Z231" t="s" s="2">
-        <v>803</v>
+        <v>80</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>80</v>
@@ -31639,19 +31494,19 @@
         <v>80</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI231" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK231" t="s" s="2">
         <v>80</v>
@@ -31666,7 +31521,7 @@
         <v>80</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>805</v>
+        <v>80</v>
       </c>
       <c r="AP231" t="s" s="2">
         <v>80</v>
@@ -31675,12 +31530,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="232" hidden="true">
+    <row r="232">
       <c r="A232" t="s" s="2">
-        <v>806</v>
+        <v>836</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>807</v>
+        <v>836</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31691,10 +31546,10 @@
         <v>81</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H232" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I232" t="s" s="2">
         <v>80</v>
@@ -31703,18 +31558,16 @@
         <v>93</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>106</v>
+        <v>250</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>808</v>
+        <v>837</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>809</v>
+        <v>838</v>
       </c>
       <c r="N232" s="2"/>
-      <c r="O232" t="s" s="2">
-        <v>810</v>
-      </c>
+      <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
         <v>80</v>
       </c>
@@ -31738,13 +31591,13 @@
         <v>80</v>
       </c>
       <c r="X232" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="Y232" t="s" s="2">
-        <v>80</v>
+        <v>839</v>
       </c>
       <c r="Z232" t="s" s="2">
-        <v>80</v>
+        <v>840</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>80</v>
@@ -31762,37 +31615,37 @@
         <v>80</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH232" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>80</v>
+        <v>841</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>80</v>
+        <v>842</v>
       </c>
       <c r="AL232" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM232" t="s" s="2">
-        <v>80</v>
+        <v>843</v>
       </c>
       <c r="AN232" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>812</v>
+        <v>80</v>
       </c>
       <c r="AP232" t="s" s="2">
-        <v>80</v>
+        <v>844</v>
       </c>
       <c r="AQ232" t="s" s="2">
         <v>80</v>
@@ -31800,10 +31653,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>813</v>
+        <v>845</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>814</v>
+        <v>845</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -31823,21 +31676,19 @@
         <v>80</v>
       </c>
       <c r="J233" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>815</v>
+        <v>107</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>816</v>
+        <v>108</v>
       </c>
       <c r="N233" s="2"/>
-      <c r="O233" t="s" s="2">
-        <v>817</v>
-      </c>
+      <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
         <v>80</v>
       </c>
@@ -31885,7 +31736,7 @@
         <v>80</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>818</v>
+        <v>109</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -31894,10 +31745,10 @@
         <v>92</v>
       </c>
       <c r="AI233" t="s" s="2">
-        <v>819</v>
+        <v>80</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK233" t="s" s="2">
         <v>80</v>
@@ -31912,7 +31763,7 @@
         <v>80</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>812</v>
+        <v>80</v>
       </c>
       <c r="AP233" t="s" s="2">
         <v>80</v>
@@ -31923,21 +31774,21 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>820</v>
+        <v>846</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H234" t="s" s="2">
         <v>80</v>
@@ -31946,23 +31797,21 @@
         <v>80</v>
       </c>
       <c r="J234" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>822</v>
+        <v>113</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>823</v>
+        <v>114</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>825</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
         <v>80</v>
       </c>
@@ -31998,31 +31847,31 @@
         <v>80</v>
       </c>
       <c r="AB234" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AC234" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AD234" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE234" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>826</v>
+        <v>119</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH234" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI234" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK234" t="s" s="2">
         <v>80</v>
@@ -32037,7 +31886,7 @@
         <v>80</v>
       </c>
       <c r="AO234" t="s" s="2">
-        <v>812</v>
+        <v>80</v>
       </c>
       <c r="AP234" t="s" s="2">
         <v>80</v>
@@ -32046,12 +31895,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -32062,30 +31911,32 @@
         <v>81</v>
       </c>
       <c r="G235" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H235" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I235" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J235" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J235" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K235" t="s" s="2">
-        <v>828</v>
+        <v>145</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>829</v>
+        <v>266</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>830</v>
+        <v>267</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="O235" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="O235" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P235" t="s" s="2">
         <v>80</v>
       </c>
@@ -32121,28 +31972,26 @@
         <v>80</v>
       </c>
       <c r="AB235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC235" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="AC235" s="2"/>
       <c r="AD235" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE235" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>827</v>
+        <v>270</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH235" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI235" t="s" s="2">
-        <v>832</v>
+        <v>80</v>
       </c>
       <c r="AJ235" t="s" s="2">
         <v>104</v>
@@ -32160,10 +32009,10 @@
         <v>80</v>
       </c>
       <c r="AO235" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="AP235" t="s" s="2">
-        <v>833</v>
+        <v>80</v>
       </c>
       <c r="AQ235" t="s" s="2">
         <v>80</v>
@@ -32171,18 +32020,20 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="C236" s="2"/>
+        <v>847</v>
+      </c>
+      <c r="C236" t="s" s="2">
+        <v>849</v>
+      </c>
       <c r="D236" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G236" t="s" s="2">
         <v>92</v>
@@ -32197,16 +32048,20 @@
         <v>93</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>228</v>
+        <v>145</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="N236" s="2"/>
-      <c r="O236" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N236" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O236" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P236" t="s" s="2">
         <v>80</v>
       </c>
@@ -32215,7 +32070,7 @@
         <v>80</v>
       </c>
       <c r="S236" t="s" s="2">
-        <v>80</v>
+        <v>851</v>
       </c>
       <c r="T236" t="s" s="2">
         <v>80</v>
@@ -32254,13 +32109,13 @@
         <v>80</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>834</v>
+        <v>270</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>80</v>
@@ -32272,7 +32127,7 @@
         <v>80</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>837</v>
+        <v>80</v>
       </c>
       <c r="AM236" t="s" s="2">
         <v>80</v>
@@ -32281,21 +32136,21 @@
         <v>80</v>
       </c>
       <c r="AO236" t="s" s="2">
-        <v>838</v>
+        <v>271</v>
       </c>
       <c r="AP236" t="s" s="2">
-        <v>839</v>
+        <v>80</v>
       </c>
       <c r="AQ236" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -32309,7 +32164,7 @@
         <v>92</v>
       </c>
       <c r="H237" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I237" t="s" s="2">
         <v>80</v>
@@ -32318,16 +32173,20 @@
         <v>93</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>841</v>
+        <v>106</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>842</v>
+        <v>308</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="N237" s="2"/>
-      <c r="O237" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N237" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O237" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P237" t="s" s="2">
         <v>80</v>
       </c>
@@ -32375,7 +32234,7 @@
         <v>80</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>840</v>
+        <v>312</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
@@ -32402,10 +32261,10 @@
         <v>80</v>
       </c>
       <c r="AO237" t="s" s="2">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="AP237" t="s" s="2">
-        <v>844</v>
+        <v>80</v>
       </c>
       <c r="AQ237" t="s" s="2">
         <v>80</v>
@@ -32413,10 +32272,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -32424,10 +32283,10 @@
       </c>
       <c r="E238" s="2"/>
       <c r="F238" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>93</v>
@@ -32439,15 +32298,17 @@
         <v>93</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="N238" s="2"/>
+        <v>856</v>
+      </c>
+      <c r="N238" t="s" s="2">
+        <v>857</v>
+      </c>
       <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
         <v>80</v>
@@ -32496,22 +32357,22 @@
         <v>80</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>80</v>
+        <v>841</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK238" t="s" s="2">
-        <v>80</v>
+        <v>858</v>
       </c>
       <c r="AL238" t="s" s="2">
         <v>80</v>
@@ -32523,10 +32384,10 @@
         <v>80</v>
       </c>
       <c r="AO238" t="s" s="2">
-        <v>848</v>
+        <v>80</v>
       </c>
       <c r="AP238" t="s" s="2">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="AQ238" t="s" s="2">
         <v>80</v>
@@ -32534,10 +32395,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -32560,13 +32421,13 @@
         <v>80</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
@@ -32617,7 +32478,7 @@
         <v>80</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>81</v>
@@ -32629,2240 +32490,32 @@
         <v>80</v>
       </c>
       <c r="AJ239" t="s" s="2">
-        <v>854</v>
+        <v>104</v>
       </c>
       <c r="AK239" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>80</v>
+        <v>863</v>
       </c>
       <c r="AM239" t="s" s="2">
-        <v>80</v>
+        <v>864</v>
       </c>
       <c r="AN239" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO239" t="s" s="2">
-        <v>80</v>
+        <v>865</v>
       </c>
       <c r="AP239" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ239" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="240" hidden="true">
-      <c r="A240" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="B240" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="C240" s="2"/>
-      <c r="D240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E240" s="2"/>
-      <c r="F240" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G240" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K240" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L240" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M240" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N240" s="2"/>
-      <c r="O240" s="2"/>
-      <c r="P240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q240" s="2"/>
-      <c r="R240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF240" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG240" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH240" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ240" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="241" hidden="true">
-      <c r="A241" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="C241" s="2"/>
-      <c r="D241" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E241" s="2"/>
-      <c r="F241" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G241" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K241" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L241" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O241" s="2"/>
-      <c r="P241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q241" s="2"/>
-      <c r="R241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF241" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG241" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH241" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ241" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ241" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="242" hidden="true">
-      <c r="A242" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C242" s="2"/>
-      <c r="D242" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="E242" s="2"/>
-      <c r="F242" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G242" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I242" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="J242" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K242" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L242" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="N242" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O242" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="P242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q242" s="2"/>
-      <c r="R242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF242" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="AG242" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH242" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ242" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ242" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="243" hidden="true">
-      <c r="A243" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="C243" s="2"/>
-      <c r="D243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E243" s="2"/>
-      <c r="F243" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G243" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K243" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="L243" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="N243" s="2"/>
-      <c r="O243" s="2"/>
-      <c r="P243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q243" s="2"/>
-      <c r="R243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X243" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y243" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="Z243" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="AA243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF243" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="AG243" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH243" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI243" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="AJ243" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN243" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="AO243" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AP243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ243" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="244" hidden="true">
-      <c r="A244" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="C244" s="2"/>
-      <c r="D244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E244" s="2"/>
-      <c r="F244" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G244" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K244" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="L244" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="M244" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="N244" s="2"/>
-      <c r="O244" s="2"/>
-      <c r="P244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q244" s="2"/>
-      <c r="R244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF244" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="AG244" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH244" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI244" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="AJ244" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ244" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="245" hidden="true">
-      <c r="A245" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="C245" s="2"/>
-      <c r="D245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E245" s="2"/>
-      <c r="F245" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G245" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K245" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="L245" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="M245" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="N245" s="2"/>
-      <c r="O245" s="2"/>
-      <c r="P245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q245" s="2"/>
-      <c r="R245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X245" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y245" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="Z245" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="AA245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF245" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="AG245" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH245" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ245" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ245" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="B246" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="C246" s="2"/>
-      <c r="D246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E246" s="2"/>
-      <c r="F246" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="G246" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H246" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K246" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="L246" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="M246" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="N246" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="O246" s="2"/>
-      <c r="P246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q246" s="2"/>
-      <c r="R246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF246" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="AG246" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH246" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ246" t="s" s="2">
-        <v>882</v>
-      </c>
-      <c r="AK246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ246" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="247" hidden="true">
-      <c r="A247" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="C247" s="2"/>
-      <c r="D247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E247" s="2"/>
-      <c r="F247" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G247" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K247" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L247" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M247" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N247" s="2"/>
-      <c r="O247" s="2"/>
-      <c r="P247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q247" s="2"/>
-      <c r="R247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF247" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG247" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH247" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ247" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="248" hidden="true">
-      <c r="A248" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="C248" s="2"/>
-      <c r="D248" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E248" s="2"/>
-      <c r="F248" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G248" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K248" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L248" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M248" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N248" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O248" s="2"/>
-      <c r="P248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q248" s="2"/>
-      <c r="R248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF248" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG248" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH248" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ248" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ248" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="249" hidden="true">
-      <c r="A249" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="C249" s="2"/>
-      <c r="D249" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="E249" s="2"/>
-      <c r="F249" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G249" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I249" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="J249" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K249" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L249" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="M249" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="N249" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O249" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="P249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q249" s="2"/>
-      <c r="R249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF249" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="AG249" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH249" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ249" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ249" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="C250" s="2"/>
-      <c r="D250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E250" s="2"/>
-      <c r="F250" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G250" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H250" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J250" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K250" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="L250" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="M250" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="N250" s="2"/>
-      <c r="O250" s="2"/>
-      <c r="P250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q250" s="2"/>
-      <c r="R250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X250" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y250" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="Z250" t="s" s="2">
-        <v>890</v>
-      </c>
-      <c r="AA250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF250" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="AG250" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH250" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI250" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="AJ250" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK250" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="AL250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM250" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="AN250" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AO250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP250" t="s" s="2">
-        <v>894</v>
-      </c>
-      <c r="AQ250" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="251" hidden="true">
-      <c r="A251" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="C251" s="2"/>
-      <c r="D251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E251" s="2"/>
-      <c r="F251" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G251" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K251" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L251" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M251" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N251" s="2"/>
-      <c r="O251" s="2"/>
-      <c r="P251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q251" s="2"/>
-      <c r="R251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF251" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG251" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH251" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ251" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="252" hidden="true">
-      <c r="A252" t="s" s="2">
-        <v>896</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>896</v>
-      </c>
-      <c r="C252" s="2"/>
-      <c r="D252" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E252" s="2"/>
-      <c r="F252" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G252" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K252" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L252" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M252" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N252" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O252" s="2"/>
-      <c r="P252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q252" s="2"/>
-      <c r="R252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB252" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC252" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE252" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF252" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG252" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH252" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ252" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ252" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="253" hidden="true">
-      <c r="A253" t="s" s="2">
-        <v>897</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>897</v>
-      </c>
-      <c r="C253" s="2"/>
-      <c r="D253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E253" s="2"/>
-      <c r="F253" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G253" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J253" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K253" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L253" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M253" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N253" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O253" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q253" s="2"/>
-      <c r="R253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB253" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AC253" s="2"/>
-      <c r="AD253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE253" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF253" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AG253" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH253" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ253" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO253" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AP253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ253" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s" s="2">
-        <v>898</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>897</v>
-      </c>
-      <c r="C254" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="D254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E254" s="2"/>
-      <c r="F254" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G254" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H254" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J254" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K254" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L254" t="s" s="2">
-        <v>900</v>
-      </c>
-      <c r="M254" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N254" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O254" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q254" s="2"/>
-      <c r="R254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S254" t="s" s="2">
-        <v>901</v>
-      </c>
-      <c r="T254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF254" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AG254" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH254" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ254" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO254" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AP254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ254" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="255" hidden="true">
-      <c r="A255" t="s" s="2">
-        <v>902</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>902</v>
-      </c>
-      <c r="C255" s="2"/>
-      <c r="D255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E255" s="2"/>
-      <c r="F255" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G255" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J255" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K255" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L255" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M255" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N255" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O255" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="P255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q255" s="2"/>
-      <c r="R255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF255" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AG255" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH255" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ255" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO255" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AP255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ255" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="B256" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="C256" s="2"/>
-      <c r="D256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E256" s="2"/>
-      <c r="F256" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="G256" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H256" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J256" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K256" t="s" s="2">
-        <v>904</v>
-      </c>
-      <c r="L256" t="s" s="2">
-        <v>905</v>
-      </c>
-      <c r="M256" t="s" s="2">
-        <v>906</v>
-      </c>
-      <c r="N256" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="O256" s="2"/>
-      <c r="P256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q256" s="2"/>
-      <c r="R256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF256" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="AG256" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH256" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI256" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="AJ256" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK256" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="AL256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP256" t="s" s="2">
-        <v>894</v>
-      </c>
-      <c r="AQ256" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="B257" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="C257" s="2"/>
-      <c r="D257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E257" s="2"/>
-      <c r="F257" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G257" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H257" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K257" t="s" s="2">
-        <v>910</v>
-      </c>
-      <c r="L257" t="s" s="2">
-        <v>911</v>
-      </c>
-      <c r="M257" t="s" s="2">
-        <v>912</v>
-      </c>
-      <c r="N257" s="2"/>
-      <c r="O257" s="2"/>
-      <c r="P257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q257" s="2"/>
-      <c r="R257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF257" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="AG257" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH257" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ257" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL257" t="s" s="2">
-        <v>913</v>
-      </c>
-      <c r="AM257" t="s" s="2">
-        <v>914</v>
-      </c>
-      <c r="AN257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO257" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="AP257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ257" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ257">
+  <autoFilter ref="A1:AQ239">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -34872,7 +32525,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI256">
+  <conditionalFormatting sqref="A2:AI238">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
